--- a/samples/phase1_alberta_data.xlsx
+++ b/samples/phase1_alberta_data.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectData" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DrillingWaste" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StorageTanks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhraseCatalog" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +567,37 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>drilling_waste_intro_selected</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>site_recon_intro_selected</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>phase2_recommendation_selected</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>executive_summary</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>drilling_waste_intro</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>site_recon_intro</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>phase2_recommendation</t>
         </is>
       </c>
     </row>
@@ -717,11 +748,41 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>option_1_aer</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>not_completed</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Ecoventure Inc. was contracted by Example Energy Ltd. to conduct a Phase I Environmental Site Assessment on the wellsite and associated facilities known as Example 4D Windy 4-4-49-4.  The well was spud 15-Mar-2004 and cased on 17-Mar-2004.  The well was re-entered in June 2004 and drilled to a total depth of 710 metres (m), and the well is currently suspended.  The well produced gas with water.
 The drilling waste was assessed using Checklist Compliance Option 1 (AER, 2014); 110 m3 of drilling waste (surface mud and fasthole mud) was disposed of via LWD at SW1/4 04-049-04 W4M, 35 m3 of mainhole drilling mud was landsprayed at SE-09-049-04 W4M, 3 m3 of shale was landspread onsite, and 60 m3 of mainhole drilling mud was hauled to the remote site at Example 10-04-048-06 W4M.
 A Phase II ESA is not required for the drilling waste.  The 2015 historical air photo shows the well centre and a possible disturbance area southeast of well centre for the containment berm and tanks.  A site visit has not been completed at this time.
 After reviewing regulatory information and records, and conducting informational interviews; it is recommended that well centre and the production areas be investigated. The Example Energy Ltd. keyword is Phase II.</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Drilling waste was managed in accordance with AER requirements. Option 1 (AER, 2014) applies to this well.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
         </is>
       </c>
     </row>
@@ -844,4 +905,137 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>phrase_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>option_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>drilling_waste_intro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>option_1_aer</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Drilling waste was managed in accordance with AER requirements. Option 1 (AER, 2014) applies to this well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>drilling_waste_intro</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Drilling waste was managed under an approved alternative disposal pathway. Details are summarized in the drilling waste table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>phase2_recommendation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>phase2_recommendation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is not recommended at this time, subject to client direction and future land use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>site_recon_intro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>not_completed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>site_recon_intro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A site visit was completed as part of this Phase I ESA. Observations from the visit are summarized below and in the site visit checklist.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/samples/phase1_alberta_data.xlsx
+++ b/samples/phase1_alberta_data.xlsx
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,100 +936,338 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drilling_waste_intro</t>
+          <t>closure_recommendation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1_aer</t>
+          <t>support_closure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Drilling waste was managed in accordance with AER requirements. Option 1 (AER, 2014) applies to this well.</t>
+          <t>Based on the data presented, Ecoventure supports proceeding with regulatory closure documentation, subject to agency review.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drilling_waste_intro</t>
+          <t>closure_recommendation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>defer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Drilling waste was managed under an approved alternative disposal pathway. Details are summarized in the drilling waste table.</t>
+          <t>Ecoventure recommends deferring closure until additional monitoring or remedial work is completed.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>phase2_recommendation</t>
+          <t>confirmatory_summary</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>met</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
+          <t>Confirmatory sampling results indicate that remedial objectives were met for the parameters and media evaluated.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>phase2_recommendation</t>
+          <t>confirmatory_summary</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>not_met</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is not recommended at this time, subject to client direction and future land use.</t>
+          <t>Confirmatory sampling results indicate that additional remedial action or monitoring is required for one or more parameters.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>site_recon_intro</t>
+          <t>drilling_waste_intro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_completed</t>
+          <t>option_1_aer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
+          <t>Drilling waste was managed in accordance with AER requirements. Option 1 (AER, 2014) applies to this well.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>drilling_waste_intro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Drilling waste was managed under an approved alternative disposal pathway. Details are summarized in the drilling waste table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>gw_data_usability</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>usable</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Field notes and laboratory quality control indicate that the groundwater data are suitable for comparison to applicable guidelines, subject to the limitations noted herein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gw_data_usability</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>qualified</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Some data limitations are noted in the field log and tables below; interpreted trends should be considered qualified where purge volumes or hold times were atypical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gw_program_intro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>This report presents results of the annual groundwater monitoring program conducted to assess groundwater quality and water levels relative to applicable Alberta guidelines and site-specific objectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gw_program_intro</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>This report summarizes baseline groundwater quality and static water levels following installation of the monitoring well network.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gw_recommendations</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ecoventure recommends continued groundwater monitoring at the established frequency to evaluate temporal trends and confirm stability of exceedances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gw_recommendations</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ecoventure recommends additional investigation of exceedances identified in this reporting period, including potential source areas and downgradient wells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gw_sampling_methods</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Groundwater samples were collected using low-flow purging and sampling methods in accordance with project-specific sampling procedures and laboratory requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gw_sampling_methods</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bailer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Groundwater samples were collected after purging each monitoring well until field parameters stabilized, using dedicated sampling equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>phase2_recommendation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>phase2_recommendation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is not recommended at this time, subject to client direction and future land use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>remediation_status</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remediation activities are ongoing at the site under an approved remedial action plan. This report summarizes confirmatory sampling and progress toward remedial objectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>remediation_status</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>confirmatory</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>This report documents confirmatory groundwater and soil sampling conducted to verify achievement of remedial objectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>site_recon_intro</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>not_completed</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>site_recon_intro</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>A site visit was completed as part of this Phase I ESA. Observations from the visit are summarized below and in the site visit checklist.</t>
         </is>

--- a/samples/phase1_alberta_data.xlsx
+++ b/samples/phase1_alberta_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,135 +467,180 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>asset_activity_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prior_reclamation_cert_number</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>site_visit_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>records_review_summary</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>interview_operator_summary</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>interview_landowner_summary</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>flare_pit_used</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>no_drilling_waste_on_site</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>site_visit_photo_notes</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>qp_names</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>spud_date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>cased_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>final_drill_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>well_depth_m</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>well_status</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>reentry</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>reentry_detail</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>production_fluid</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>aer_waste_compliance_option</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>drilling_waste_summary</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>phase2_drilling_waste_required</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>phase2_esa_required</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>client_phase_keyword</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>site_visit_completed</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>air_photo_observations</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>investigations_recommended</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>infrastructure_summary</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>spills_releases</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>conclusions_recommendations</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>drilling_waste_intro_selected</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>site_recon_intro_selected</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>phase2_recommendation_selected</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>executive_summary</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>drilling_waste_intro</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>site_recon_intro</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>phase2_recommendation</t>
         </is>
@@ -649,120 +694,149 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>Oil well site — drilled and abandoned / suspended</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Company well file, AER spills search, ABADATA, and historical air photos reviewed.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Informational interview with former site operator regarding waste disposal and infrastructure.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>Ecoventure QP (P.Eng.); Ecoventure QP (R.T.Ag.)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>15-Mar-2004</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>17-Mar-2004</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>19-Jun-2004</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>The well was re-entered in June 2004 and drilled to a total depth of 710 metres (m), and the well is currently suspended</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>gas with water</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Option 1 (AER, 2014)</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>110 m3 of drilling waste (surface mud and fasthole mud) was disposed of via LWD at SW1/4 04-049-04 W4M, 35 m3 of mainhole drilling mud was landsprayed at SE-09-049-04 W4M, 3 m3 of shale was landspread onsite, and 60 m3 of mainhole drilling mud was hauled to the remote site at Example 10-04-048-06 W4M</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Phase II</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>The 2015 historical air photo shows the well centre and a possible disturbance area southeast of well centre for the containment berm and tanks</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>well centre and the production areas be investigated</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Access road, teardrop, wellhead, containment berm for production tanks</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>Investigate well centre and production areas. Phase II ESA recommended.</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>option_1_aer</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>not_completed</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Ecoventure Inc. was contracted by Example Energy Ltd. to conduct a Phase I Environmental Site Assessment on the wellsite and associated facilities known as Example 4D Windy 4-4-49-4.  The well was spud 15-Mar-2004 and cased on 17-Mar-2004.  The well was re-entered in June 2004 and drilled to a total depth of 710 metres (m), and the well is currently suspended.  The well produced gas with water.
 The drilling waste was assessed using Checklist Compliance Option 1 (AER, 2014); 110 m3 of drilling waste (surface mud and fasthole mud) was disposed of via LWD at SW1/4 04-049-04 W4M, 35 m3 of mainhole drilling mud was landsprayed at SE-09-049-04 W4M, 3 m3 of shale was landspread onsite, and 60 m3 of mainhole drilling mud was hauled to the remote site at Example 10-04-048-06 W4M.
@@ -770,17 +844,17 @@
 After reviewing regulatory information and records, and conducting informational interviews; it is recommended that well centre and the production areas be investigated. The Example Energy Ltd. keyword is Phase II.</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>Drilling waste was managed in accordance with AER requirements. Option 1 (AER, 2014) applies to this well.</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
         </is>
@@ -797,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,6 +895,36 @@
           <t>location</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>disposal_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>gps_coordinates</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sump_depth_m</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cover_depth_m</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>remote_cert_number</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>waste_manifest_refs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -843,6 +947,16 @@
           <t>SW1/4 04-049-04 W4M; SE-09-049-04 W4M; onsite; remote site</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>off-lease and on-lease</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/phase1_alberta_data.xlsx
+++ b/samples/phase1_alberta_data.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectData" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DrillingWaste" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StorageTanks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhraseCatalog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DwdaChecklist" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StorageTanks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhraseCatalog" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS2"/>
+  <dimension ref="A1:AW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,75 +573,95 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>cuttings_volume_on_lease_m3</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>directive_050_notification_ref</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>dwda_salinity_pathway</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>dwda_phase2_required</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>phase2_esa_required</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>client_phase_keyword</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>site_visit_completed</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>air_photo_observations</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>investigations_recommended</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>infrastructure_summary</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>spills_releases</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>conclusions_recommendations</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>drilling_waste_intro_selected</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>site_recon_intro_selected</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>phase2_recommendation_selected</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>executive_summary</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>drilling_waste_intro</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>site_recon_intro</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>phase2_recommendation</t>
         </is>
@@ -783,78 +804,99 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Directive 050 notification on file; tour reports reviewed</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>equivalent_salinity</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Phase II</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>The 2015 historical air photo shows the well centre and a possible disturbance area southeast of well centre for the containment berm and tanks</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>well centre and the production areas be investigated</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>Access road, teardrop, wellhead, containment berm for production tanks</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Investigate well centre and production areas. Phase II ESA recommended.</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>option_1_aer</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>not_completed</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>Ecoventure Inc. was contracted by Example Energy Ltd. to conduct a Phase I Environmental Site Assessment on the wellsite and associated facilities known as Example 4D Windy 4-4-49-4.  The well was spud 15-Mar-2004 and cased on 17-Mar-2004.  The well was re-entered in June 2004 and drilled to a total depth of 710 metres (m), and the well is currently suspended.  The well produced gas with water.
 The drilling waste was assessed using Checklist Compliance Option 1 (AER, 2014); 110 m3 of drilling waste (surface mud and fasthole mud) was disposed of via LWD at SW1/4 04-049-04 W4M, 35 m3 of mainhole drilling mud was landsprayed at SE-09-049-04 W4M, 3 m3 of shale was landspread onsite, and 60 m3 of mainhole drilling mud was hauled to the remote site at Example 10-04-048-06 W4M.
+Salinity within disposal areas may be assessed using Equivalent Salinity Guidelines; other parameters must meet Alberta Tier 1/2.
 A Phase II ESA is not required for the drilling waste.  The 2015 historical air photo shows the well centre and a possible disturbance area southeast of well centre for the containment berm and tanks.  A site visit has not been completed at this time.
 After reviewing regulatory information and records, and conducting informational interviews; it is recommended that well centre and the production areas be investigated. The Example Energy Ltd. keyword is Phase II.</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>Drilling waste was managed in accordance with AER requirements. Option 1 (AER, 2014) applies to this well.</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
         </is>
@@ -871,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +967,21 @@
           <t>waste_manifest_refs</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dwda_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>area_m2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>salinity_exceedance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -934,29 +991,138 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LWD, landspray, landspread onsite, remote site</t>
+          <t>LWD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SW1/4 04-049-04 W4M; SE-09-049-04 W4M; onsite; remote site</t>
+          <t>SW1/4 04-049-04 W4M well centre</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>off-lease and on-lease</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>on-lease</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>51.1234,-114.5678</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>DWDA-1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mainhole mud</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>landspray</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SE-09-049-04 W4M</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>off-lease</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Manifest 2017-042</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mainhole mud</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>remote haul</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Example 10-04-048-06 W4M remote site</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>off-lease</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RC-2017-009</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Manifest 2017-043</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -969,50 +1135,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>tank_type</t>
+          <t>checklist_item_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>response</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>capacity_m3</t>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Above ground tank</t>
+          <t>d050.notification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Produced water</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SE of well centre</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Tour report on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>d050.compliance_option</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Option 1 AER 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>d050.waste_summary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>d050.waste_table</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Three disposal events in DrillingWaste</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>d050.cuttings_volume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>110 m3 LWD on lease</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>d050.gps_on_lease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>d050.salinity_pathway</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Equivalent Salinity within DWDA-1</t>
         </is>
       </c>
     </row>
@@ -1027,29 +1277,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>phrase_key</t>
+          <t>tank_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>content</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>capacity_m3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Above ground tank</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Produced water</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SE of well centre</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>phrase_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>option_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>closure_recommendation</t>
         </is>
       </c>
@@ -1145,243 +1453,311 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Drilling waste was managed under an approved alternative disposal pathway. Details are summarized in the drilling waste table.</t>
+          <t>Drilling waste was managed under Checklist Compliance Option 2. Calculation tables are provided in Appendix G.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gw_data_usability</t>
+          <t>drilling_waste_intro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>usable</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Field notes and laboratory quality control indicate that the groundwater data are suitable for comparison to applicable guidelines, subject to the limitations noted herein.</t>
+          <t>Drilling waste disposal areas were assessed under Compliance Option 3 per Assessing Drilling Waste Disposal Areas guidance.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gw_data_usability</t>
+          <t>drilling_waste_intro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>qualified</t>
+          <t>approved_facility</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Some data limitations are noted in the field log and tables below; interpreted trends should be considered qualified where purge volumes or hold times were atypical.</t>
+          <t>All drilling waste was managed at an AER-approved waste management facility. On-lease DWDA assessment is limited to documentation review.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gw_program_intro</t>
+          <t>dwda_salinity_note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>equivalent_salinity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>This report presents results of the annual groundwater monitoring program conducted to assess groundwater quality and water levels relative to applicable Alberta guidelines and site-specific objectives.</t>
+          <t>Salinity within each drilling waste disposal area may be assessed using Equivalent Salinity Guidelines. Hydrocarbons, metals, and other contaminants within the DWDA and across the remainder of the lease must meet Alberta Tier 1 or Tier 2 remediation guidelines.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gw_program_intro</t>
+          <t>dwda_salinity_note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>pending_phase2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>This report summarizes baseline groundwater quality and static water levels following installation of the monitoring well network.</t>
+          <t>Salinity and other contaminants within identified disposal areas require Phase II sampling and comparison to Equivalent Salinity (salinity) and Alberta Tier 1/2 guidelines (other parameters) before reclamation certification.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gw_recommendations</t>
+          <t>gw_data_usability</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>usable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecoventure recommends continued groundwater monitoring at the established frequency to evaluate temporal trends and confirm stability of exceedances.</t>
+          <t>Field notes and laboratory quality control indicate that the groundwater data are suitable for comparison to applicable guidelines, subject to the limitations noted herein.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gw_recommendations</t>
+          <t>gw_data_usability</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>investigate</t>
+          <t>qualified</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecoventure recommends additional investigation of exceedances identified in this reporting period, including potential source areas and downgradient wells.</t>
+          <t>Some data limitations are noted in the field log and tables below; interpreted trends should be considered qualified where purge volumes or hold times were atypical.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gw_sampling_methods</t>
+          <t>gw_program_intro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>low_flow</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Groundwater samples were collected using low-flow purging and sampling methods in accordance with project-specific sampling procedures and laboratory requirements.</t>
+          <t>This report presents results of the annual groundwater monitoring program conducted to assess groundwater quality and water levels relative to applicable Alberta guidelines and site-specific objectives.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gw_sampling_methods</t>
+          <t>gw_program_intro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bailer</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Groundwater samples were collected after purging each monitoring well until field parameters stabilized, using dedicated sampling equipment.</t>
+          <t>This report summarizes baseline groundwater quality and static water levels following installation of the monitoring well network.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>phase2_recommendation</t>
+          <t>gw_recommendations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>continue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
+          <t>Ecoventure recommends continued groundwater monitoring at the established frequency to evaluate temporal trends and confirm stability of exceedances.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>phase2_recommendation</t>
+          <t>gw_recommendations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>investigate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is not recommended at this time, subject to client direction and future land use.</t>
+          <t>Ecoventure recommends additional investigation of exceedances identified in this reporting period, including potential source areas and downgradient wells.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>remediation_status</t>
+          <t>gw_sampling_methods</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>low_flow</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remediation activities are ongoing at the site under an approved remedial action plan. This report summarizes confirmatory sampling and progress toward remedial objectives.</t>
+          <t>Groundwater samples were collected using low-flow purging and sampling methods in accordance with project-specific sampling procedures and laboratory requirements.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>remediation_status</t>
+          <t>gw_sampling_methods</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>confirmatory</t>
+          <t>bailer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>This report documents confirmatory groundwater and soil sampling conducted to verify achievement of remedial objectives.</t>
+          <t>Groundwater samples were collected after purging each monitoring well until field parameters stabilized, using dedicated sampling equipment.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>site_recon_intro</t>
+          <t>phase2_recommendation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_completed</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
+          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is recommended to further evaluate identified areas of potential environmental concern.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>phase2_recommendation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is not recommended at this time, subject to client direction and future land use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>remediation_status</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remediation activities are ongoing at the site under an approved remedial action plan. This report summarizes confirmatory sampling and progress toward remedial objectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>remediation_status</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>confirmatory</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>This report documents confirmatory groundwater and soil sampling conducted to verify achievement of remedial objectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>site_recon_intro</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>not_completed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A site visit was not completed as part of this Phase I ESA. Findings are based on available records, regulatory databases, and historical air photo review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>site_recon_intro</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>A site visit was completed as part of this Phase I ESA. Observations from the visit are summarized below and in the site visit checklist.</t>
         </is>

--- a/samples/phase1_alberta_data.xlsx
+++ b/samples/phase1_alberta_data.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DrillingWaste" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DwdaChecklist" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StorageTanks" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhraseCatalog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apecs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhraseCatalog" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1335,6 +1336,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>apec_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>apec_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>location_description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>concern_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_of_concern</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>evidence_summary</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>source_document</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>phase2_recommended</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>APEC-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Historical flare pit</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SW corner of lease</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>flare_pit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>air_photo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Air photos show former flare pit depression.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>appendix_c_air_photos.pdf</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sample for confirmation if Phase II proceeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>APEC-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Produced water tank berm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SE of well centre</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>storage_tank</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>records</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Above-ground produced water tank noted in records.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>historical_phase1.pdf</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
